--- a/countries/cn-jx/2000-2004.xlsx
+++ b/countries/cn-jx/2000-2004.xlsx
@@ -765,9 +765,12 @@
       <c r="O2" t="n">
         <v>1</v>
       </c>
+      <c r="R2" t="n">
+        <v>0.002334267040149393</v>
+      </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -1155,9 +1158,12 @@
       <c r="O4" t="n">
         <v>298</v>
       </c>
+      <c r="R4" t="n">
+        <v>0.6956115779645192</v>
+      </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -1545,9 +1551,12 @@
       <c r="O6" t="n">
         <v>3049</v>
       </c>
+      <c r="R6" t="n">
+        <v>7.1171802054155</v>
+      </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1935,9 +1944,12 @@
       <c r="O8" t="n">
         <v>26</v>
       </c>
+      <c r="R8" t="n">
+        <v>0.06069094304388423</v>
+      </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -2325,9 +2337,12 @@
       <c r="O10" t="n">
         <v>20</v>
       </c>
+      <c r="R10" t="n">
+        <v>0.04668534080298786</v>
+      </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -2715,9 +2730,12 @@
       <c r="O12" t="n">
         <v>1</v>
       </c>
+      <c r="R12" t="n">
+        <v>0.002334267040149393</v>
+      </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -3105,9 +3123,12 @@
       <c r="O14" t="n">
         <v>523</v>
       </c>
+      <c r="R14" t="n">
+        <v>1.220821661998132</v>
+      </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -3495,9 +3516,12 @@
       <c r="O16" t="n">
         <v>3619</v>
       </c>
+      <c r="R16" t="n">
+        <v>8.447712418300654</v>
+      </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -3885,9 +3909,12 @@
       <c r="O18" t="n">
         <v>134</v>
       </c>
+      <c r="R18" t="n">
+        <v>0.3127917833800187</v>
+      </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -4275,9 +4302,12 @@
       <c r="O20" t="n">
         <v>19</v>
       </c>
+      <c r="R20" t="n">
+        <v>0.04435107376283847</v>
+      </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -4665,9 +4695,12 @@
       <c r="O22" t="n">
         <v>529</v>
       </c>
+      <c r="R22" t="n">
+        <v>1.234827264239029</v>
+      </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -5055,9 +5088,12 @@
       <c r="O24" t="n">
         <v>109</v>
       </c>
+      <c r="R24" t="n">
+        <v>0.2544351073762838</v>
+      </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -5445,9 +5481,12 @@
       <c r="O26" t="n">
         <v>1</v>
       </c>
+      <c r="R26" t="n">
+        <v>0.002334267040149393</v>
+      </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -5835,9 +5874,12 @@
       <c r="O28" t="n">
         <v>249</v>
       </c>
+      <c r="R28" t="n">
+        <v>0.5812324929971988</v>
+      </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -6225,9 +6267,12 @@
       <c r="O30" t="n">
         <v>12</v>
       </c>
+      <c r="R30" t="n">
+        <v>0.02801120448179272</v>
+      </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -6615,9 +6660,12 @@
       <c r="O32" t="n">
         <v>10</v>
       </c>
+      <c r="R32" t="n">
+        <v>0.02334267040149393</v>
+      </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -7005,9 +7053,12 @@
       <c r="O34" t="n">
         <v>404</v>
       </c>
+      <c r="R34" t="n">
+        <v>0.9430438842203548</v>
+      </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -7395,9 +7446,12 @@
       <c r="O36" t="n">
         <v>26</v>
       </c>
+      <c r="R36" t="n">
+        <v>0.06069094304388423</v>
+      </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -7785,9 +7839,12 @@
       <c r="O38" t="n">
         <v>3</v>
       </c>
+      <c r="R38" t="n">
+        <v>0.00700280112044818</v>
+      </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -8175,9 +8232,12 @@
       <c r="O40" t="n">
         <v>388</v>
       </c>
+      <c r="R40" t="n">
+        <v>0.9056956115779645</v>
+      </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -8565,9 +8625,12 @@
       <c r="O42" t="n">
         <v>3003</v>
       </c>
+      <c r="R42" t="n">
+        <v>7.009803921568627</v>
+      </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -8955,9 +9018,12 @@
       <c r="O44" t="n">
         <v>41</v>
       </c>
+      <c r="R44" t="n">
+        <v>0.09570494864612512</v>
+      </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -9345,9 +9411,12 @@
       <c r="O46" t="n">
         <v>30</v>
       </c>
+      <c r="R46" t="n">
+        <v>0.07002801120448179</v>
+      </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -9735,9 +9804,12 @@
       <c r="O48" t="n">
         <v>507</v>
       </c>
+      <c r="R48" t="n">
+        <v>1.183473389355742</v>
+      </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -10125,9 +10197,12 @@
       <c r="O50" t="n">
         <v>3046</v>
       </c>
+      <c r="R50" t="n">
+        <v>7.110177404295051</v>
+      </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -10515,9 +10590,12 @@
       <c r="O52" t="n">
         <v>116</v>
       </c>
+      <c r="R52" t="n">
+        <v>0.2707749766573296</v>
+      </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -10905,9 +10983,12 @@
       <c r="O54" t="n">
         <v>24</v>
       </c>
+      <c r="R54" t="n">
+        <v>0.05602240896358544</v>
+      </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -11295,9 +11376,12 @@
       <c r="O56" t="n">
         <v>521</v>
       </c>
+      <c r="R56" t="n">
+        <v>1.216153127917834</v>
+      </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -11685,9 +11769,12 @@
       <c r="O58" t="n">
         <v>115</v>
       </c>
+      <c r="R58" t="n">
+        <v>0.2684407096171802</v>
+      </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -12075,9 +12162,12 @@
       <c r="O60" t="n">
         <v>2</v>
       </c>
+      <c r="R60" t="n">
+        <v>0.004668534080298786</v>
+      </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -12465,9 +12555,12 @@
       <c r="O62" t="n">
         <v>177</v>
       </c>
+      <c r="R62" t="n">
+        <v>0.4131652661064426</v>
+      </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -12855,9 +12948,12 @@
       <c r="O64" t="n">
         <v>28</v>
       </c>
+      <c r="R64" t="n">
+        <v>0.06535947712418301</v>
+      </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -13245,9 +13341,12 @@
       <c r="O66" t="n">
         <v>14</v>
       </c>
+      <c r="R66" t="n">
+        <v>0.03267973856209151</v>
+      </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -13635,9 +13734,12 @@
       <c r="O68" t="n">
         <v>390</v>
       </c>
+      <c r="R68" t="n">
+        <v>0.9103641456582633</v>
+      </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -14025,9 +14127,12 @@
       <c r="O70" t="n">
         <v>26</v>
       </c>
+      <c r="R70" t="n">
+        <v>0.06069094304388423</v>
+      </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -14415,9 +14520,12 @@
       <c r="O72" t="n">
         <v>3</v>
       </c>
+      <c r="R72" t="n">
+        <v>0.00700280112044818</v>
+      </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -14805,9 +14913,12 @@
       <c r="O74" t="n">
         <v>412</v>
       </c>
+      <c r="R74" t="n">
+        <v>0.96171802054155</v>
+      </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -15195,9 +15306,12 @@
       <c r="O76" t="n">
         <v>3290</v>
       </c>
+      <c r="R76" t="n">
+        <v>7.679738562091504</v>
+      </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -15585,9 +15699,12 @@
       <c r="O78" t="n">
         <v>47</v>
       </c>
+      <c r="R78" t="n">
+        <v>0.1097105508870215</v>
+      </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -15975,9 +16092,12 @@
       <c r="O80" t="n">
         <v>38</v>
       </c>
+      <c r="R80" t="n">
+        <v>0.08870214752567694</v>
+      </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -16365,9 +16485,12 @@
       <c r="O82" t="n">
         <v>4</v>
       </c>
+      <c r="R82" t="n">
+        <v>0.009337068160597572</v>
+      </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -16755,9 +16878,12 @@
       <c r="O84" t="n">
         <v>594</v>
       </c>
+      <c r="R84" t="n">
+        <v>1.38655462184874</v>
+      </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -17145,9 +17271,12 @@
       <c r="O86" t="n">
         <v>3477</v>
       </c>
+      <c r="R86" t="n">
+        <v>8.116246498599441</v>
+      </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -17535,9 +17664,12 @@
       <c r="O88" t="n">
         <v>116</v>
       </c>
+      <c r="R88" t="n">
+        <v>0.2707749766573296</v>
+      </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
@@ -17925,9 +18057,12 @@
       <c r="O90" t="n">
         <v>12</v>
       </c>
+      <c r="R90" t="n">
+        <v>0.02801120448179272</v>
+      </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
@@ -18315,9 +18450,12 @@
       <c r="O92" t="n">
         <v>562</v>
       </c>
+      <c r="R92" t="n">
+        <v>1.311858076563959</v>
+      </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
@@ -18705,9 +18843,12 @@
       <c r="O94" t="n">
         <v>113</v>
       </c>
+      <c r="R94" t="n">
+        <v>0.2637721755368814</v>
+      </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
@@ -19095,9 +19236,12 @@
       <c r="O96" t="n">
         <v>2</v>
       </c>
+      <c r="R96" t="n">
+        <v>0.004668534080298786</v>
+      </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
@@ -19485,9 +19629,12 @@
       <c r="O98" t="n">
         <v>584</v>
       </c>
+      <c r="R98" t="n">
+        <v>1.363211951447246</v>
+      </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
@@ -19875,9 +20022,12 @@
       <c r="O100" t="n">
         <v>76</v>
       </c>
+      <c r="R100" t="n">
+        <v>0.1774042950513539</v>
+      </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
@@ -20265,9 +20415,12 @@
       <c r="O102" t="n">
         <v>14</v>
       </c>
+      <c r="R102" t="n">
+        <v>0.03267973856209151</v>
+      </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
@@ -20655,9 +20808,12 @@
       <c r="O104" t="n">
         <v>285</v>
       </c>
+      <c r="R104" t="n">
+        <v>0.665266106442577</v>
+      </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
@@ -21045,9 +21201,12 @@
       <c r="O106" t="n">
         <v>23</v>
       </c>
+      <c r="R106" t="n">
+        <v>0.05368814192343604</v>
+      </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
@@ -21435,9 +21594,12 @@
       <c r="O108" t="n">
         <v>5</v>
       </c>
+      <c r="R108" t="n">
+        <v>0.01167133520074697</v>
+      </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
@@ -21825,9 +21987,12 @@
       <c r="O110" t="n">
         <v>353</v>
       </c>
+      <c r="R110" t="n">
+        <v>0.8239962651727358</v>
+      </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
@@ -22215,9 +22380,12 @@
       <c r="O112" t="n">
         <v>3230</v>
       </c>
+      <c r="R112" t="n">
+        <v>7.53968253968254</v>
+      </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
@@ -22605,9 +22773,12 @@
       <c r="O114" t="n">
         <v>44</v>
       </c>
+      <c r="R114" t="n">
+        <v>0.1027077497665733</v>
+      </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
@@ -22995,9 +23166,12 @@
       <c r="O116" t="n">
         <v>28</v>
       </c>
+      <c r="R116" t="n">
+        <v>0.06535947712418301</v>
+      </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U116" t="inlineStr">
@@ -23385,9 +23559,12 @@
       <c r="O118" t="n">
         <v>6</v>
       </c>
+      <c r="R118" t="n">
+        <v>0.01400560224089636</v>
+      </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U118" t="inlineStr">
@@ -23775,9 +23952,12 @@
       <c r="O120" t="n">
         <v>1151</v>
       </c>
+      <c r="R120" t="n">
+        <v>2.686741363211952</v>
+      </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U120" t="inlineStr">
@@ -24165,9 +24345,12 @@
       <c r="O122" t="n">
         <v>3736</v>
       </c>
+      <c r="R122" t="n">
+        <v>8.720821661998132</v>
+      </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U122" t="inlineStr">
@@ -24555,9 +24738,12 @@
       <c r="O124" t="n">
         <v>131</v>
       </c>
+      <c r="R124" t="n">
+        <v>0.3057889822595705</v>
+      </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U124" t="inlineStr">
@@ -24945,9 +25131,12 @@
       <c r="O126" t="n">
         <v>13</v>
       </c>
+      <c r="R126" t="n">
+        <v>0.03034547152194211</v>
+      </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U126" t="inlineStr">
@@ -25335,9 +25524,12 @@
       <c r="O128" t="n">
         <v>2</v>
       </c>
+      <c r="R128" t="n">
+        <v>0.004668534080298786</v>
+      </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U128" t="inlineStr">
@@ -25725,9 +25917,12 @@
       <c r="O130" t="n">
         <v>580</v>
       </c>
+      <c r="R130" t="n">
+        <v>1.353874883286648</v>
+      </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U130" t="inlineStr">
@@ -26115,9 +26310,12 @@
       <c r="O132" t="n">
         <v>144</v>
       </c>
+      <c r="R132" t="n">
+        <v>0.3361344537815126</v>
+      </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U132" t="inlineStr">
@@ -26505,9 +26703,12 @@
       <c r="O134" t="n">
         <v>1</v>
       </c>
+      <c r="R134" t="n">
+        <v>0.002334267040149393</v>
+      </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U134" t="inlineStr">
@@ -26895,9 +27096,12 @@
       <c r="O136" t="n">
         <v>914</v>
       </c>
+      <c r="R136" t="n">
+        <v>2.133520074696545</v>
+      </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U136" t="inlineStr">
@@ -27285,9 +27489,12 @@
       <c r="O138" t="n">
         <v>144</v>
       </c>
+      <c r="R138" t="n">
+        <v>0.3361344537815126</v>
+      </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U138" t="inlineStr">
@@ -27675,9 +27882,12 @@
       <c r="O140" t="n">
         <v>18</v>
       </c>
+      <c r="R140" t="n">
+        <v>0.04201680672268908</v>
+      </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U140" t="inlineStr">
@@ -28065,9 +28275,12 @@
       <c r="O142" t="n">
         <v>490</v>
       </c>
+      <c r="R142" t="n">
+        <v>1.143790849673203</v>
+      </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U142" t="inlineStr">
@@ -28455,9 +28668,12 @@
       <c r="O144" t="n">
         <v>27</v>
       </c>
+      <c r="R144" t="n">
+        <v>0.06302521008403361</v>
+      </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U144" t="inlineStr">
@@ -28845,9 +29061,12 @@
       <c r="O146" t="n">
         <v>3</v>
       </c>
+      <c r="R146" t="n">
+        <v>0.00700280112044818</v>
+      </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U146" t="inlineStr">
@@ -29235,9 +29454,12 @@
       <c r="O148" t="n">
         <v>355</v>
       </c>
+      <c r="R148" t="n">
+        <v>0.8286647992530346</v>
+      </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U148" t="inlineStr">
@@ -29625,9 +29847,12 @@
       <c r="O150" t="n">
         <v>3099</v>
       </c>
+      <c r="R150" t="n">
+        <v>7.23389355742297</v>
+      </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U150" t="inlineStr">
@@ -30015,9 +30240,12 @@
       <c r="O152" t="n">
         <v>47</v>
       </c>
+      <c r="R152" t="n">
+        <v>0.1097105508870215</v>
+      </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U152" t="inlineStr">
@@ -30405,9 +30633,12 @@
       <c r="O154" t="n">
         <v>16</v>
       </c>
+      <c r="R154" t="n">
+        <v>0.03734827264239029</v>
+      </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U154" t="inlineStr">
@@ -30795,9 +31026,12 @@
       <c r="O156" t="n">
         <v>1876</v>
       </c>
+      <c r="R156" t="n">
+        <v>4.379084967320261</v>
+      </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U156" t="inlineStr">
@@ -31185,9 +31419,12 @@
       <c r="O158" t="n">
         <v>3501</v>
       </c>
+      <c r="R158" t="n">
+        <v>8.172268907563026</v>
+      </c>
       <c r="S158" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U158" t="inlineStr">
@@ -31575,9 +31812,12 @@
       <c r="O160" t="n">
         <v>190</v>
       </c>
+      <c r="R160" t="n">
+        <v>0.4435107376283847</v>
+      </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U160" t="inlineStr">
@@ -31965,9 +32205,12 @@
       <c r="O162" t="n">
         <v>15</v>
       </c>
+      <c r="R162" t="n">
+        <v>0.0350140056022409</v>
+      </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U162" t="inlineStr">
@@ -32355,9 +32598,12 @@
       <c r="O164" t="n">
         <v>620</v>
       </c>
+      <c r="R164" t="n">
+        <v>1.447245564892624</v>
+      </c>
       <c r="S164" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U164" t="inlineStr">
@@ -32745,9 +32991,12 @@
       <c r="O166" t="n">
         <v>128</v>
       </c>
+      <c r="R166" t="n">
+        <v>0.2987861811391223</v>
+      </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U166" t="inlineStr">
@@ -33135,9 +33384,12 @@
       <c r="O168" t="n">
         <v>1</v>
       </c>
+      <c r="R168" t="n">
+        <v>0.002334267040149393</v>
+      </c>
       <c r="S168" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U168" t="inlineStr">
@@ -33525,9 +33777,12 @@
       <c r="O170" t="n">
         <v>1070</v>
       </c>
+      <c r="R170" t="n">
+        <v>2.497665732959851</v>
+      </c>
       <c r="S170" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U170" t="inlineStr">
@@ -33915,9 +34170,12 @@
       <c r="O172" t="n">
         <v>68</v>
       </c>
+      <c r="R172" t="n">
+        <v>0.1587301587301587</v>
+      </c>
       <c r="S172" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U172" t="inlineStr">
@@ -34305,9 +34563,12 @@
       <c r="O174" t="n">
         <v>25</v>
       </c>
+      <c r="R174" t="n">
+        <v>0.05835667600373483</v>
+      </c>
       <c r="S174" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U174" t="inlineStr">
@@ -34695,9 +34956,12 @@
       <c r="O176" t="n">
         <v>1000</v>
       </c>
+      <c r="R176" t="n">
+        <v>2.334267040149393</v>
+      </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U176" t="inlineStr">
@@ -35085,9 +35349,12 @@
       <c r="O178" t="n">
         <v>30</v>
       </c>
+      <c r="R178" t="n">
+        <v>0.07002801120448179</v>
+      </c>
       <c r="S178" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U178" t="inlineStr">
@@ -35475,9 +35742,12 @@
       <c r="O180" t="n">
         <v>4</v>
       </c>
+      <c r="R180" t="n">
+        <v>0.009337068160597572</v>
+      </c>
       <c r="S180" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U180" t="inlineStr">
@@ -35865,9 +36135,12 @@
       <c r="O182" t="n">
         <v>299</v>
       </c>
+      <c r="R182" t="n">
+        <v>0.6979458450046686</v>
+      </c>
       <c r="S182" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U182" t="inlineStr">
@@ -36255,9 +36528,12 @@
       <c r="O184" t="n">
         <v>2932</v>
       </c>
+      <c r="R184" t="n">
+        <v>6.84407096171802</v>
+      </c>
       <c r="S184" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U184" t="inlineStr">
@@ -36645,9 +36921,12 @@
       <c r="O186" t="n">
         <v>55</v>
       </c>
+      <c r="R186" t="n">
+        <v>0.1283846872082166</v>
+      </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U186" t="inlineStr">
@@ -37035,9 +37314,12 @@
       <c r="O188" t="n">
         <v>18</v>
       </c>
+      <c r="R188" t="n">
+        <v>0.04201680672268908</v>
+      </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U188" t="inlineStr">
@@ -37425,9 +37707,12 @@
       <c r="O190" t="n">
         <v>32</v>
       </c>
+      <c r="R190" t="n">
+        <v>0.07469654528478058</v>
+      </c>
       <c r="S190" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U190" t="inlineStr">
@@ -37815,9 +38100,12 @@
       <c r="O192" t="n">
         <v>1698</v>
       </c>
+      <c r="R192" t="n">
+        <v>3.96358543417367</v>
+      </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U192" t="inlineStr">
@@ -38205,9 +38493,12 @@
       <c r="O194" t="n">
         <v>3563</v>
       </c>
+      <c r="R194" t="n">
+        <v>8.316993464052286</v>
+      </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U194" t="inlineStr">
@@ -38595,9 +38886,12 @@
       <c r="O196" t="n">
         <v>222</v>
       </c>
+      <c r="R196" t="n">
+        <v>0.5182072829131653</v>
+      </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U196" t="inlineStr">
@@ -38985,9 +39279,12 @@
       <c r="O198" t="n">
         <v>18</v>
       </c>
+      <c r="R198" t="n">
+        <v>0.04201680672268908</v>
+      </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U198" t="inlineStr">
@@ -39375,9 +39672,12 @@
       <c r="O200" t="n">
         <v>1</v>
       </c>
+      <c r="R200" t="n">
+        <v>0.002334267040149393</v>
+      </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U200" t="inlineStr">
@@ -39765,9 +40065,12 @@
       <c r="O202" t="n">
         <v>592</v>
       </c>
+      <c r="R202" t="n">
+        <v>1.381886087768441</v>
+      </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U202" t="inlineStr">
@@ -40155,9 +40458,12 @@
       <c r="O204" t="n">
         <v>181</v>
       </c>
+      <c r="R204" t="n">
+        <v>0.4225023342670401</v>
+      </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U204" t="inlineStr">
@@ -40545,9 +40851,12 @@
       <c r="O206" t="n">
         <v>3</v>
       </c>
+      <c r="R206" t="n">
+        <v>0.00700280112044818</v>
+      </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U206" t="inlineStr">
@@ -40935,9 +41244,12 @@
       <c r="O208" t="n">
         <v>1323</v>
       </c>
+      <c r="R208" t="n">
+        <v>3.088235294117647</v>
+      </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U208" t="inlineStr">
@@ -41325,9 +41637,12 @@
       <c r="O210" t="n">
         <v>100</v>
       </c>
+      <c r="R210" t="n">
+        <v>0.2334267040149393</v>
+      </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U210" t="inlineStr">
@@ -41715,9 +42030,12 @@
       <c r="O212" t="n">
         <v>22</v>
       </c>
+      <c r="R212" t="n">
+        <v>0.05135387488328665</v>
+      </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U212" t="inlineStr">
@@ -42105,9 +42423,12 @@
       <c r="O214" t="n">
         <v>1064</v>
       </c>
+      <c r="R214" t="n">
+        <v>2.483660130718954</v>
+      </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U214" t="inlineStr">
@@ -42495,9 +42816,12 @@
       <c r="O216" t="n">
         <v>22</v>
       </c>
+      <c r="R216" t="n">
+        <v>0.05135387488328665</v>
+      </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U216" t="inlineStr">
@@ -42885,9 +43209,12 @@
       <c r="O218" t="n">
         <v>3</v>
       </c>
+      <c r="R218" t="n">
+        <v>0.00700280112044818</v>
+      </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U218" t="inlineStr">
@@ -43275,9 +43602,12 @@
       <c r="O220" t="n">
         <v>306</v>
       </c>
+      <c r="R220" t="n">
+        <v>0.7142857142857143</v>
+      </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U220" t="inlineStr">
@@ -43665,9 +43995,12 @@
       <c r="O222" t="n">
         <v>3076</v>
       </c>
+      <c r="R222" t="n">
+        <v>7.180205415499533</v>
+      </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U222" t="inlineStr">
@@ -44055,9 +44388,12 @@
       <c r="O224" t="n">
         <v>59</v>
       </c>
+      <c r="R224" t="n">
+        <v>0.1377217553688142</v>
+      </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U224" t="inlineStr">
@@ -44445,9 +44781,12 @@
       <c r="O226" t="n">
         <v>10</v>
       </c>
+      <c r="R226" t="n">
+        <v>0.02334267040149393</v>
+      </c>
       <c r="S226" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U226" t="inlineStr">
@@ -44835,9 +45174,12 @@
       <c r="O228" t="n">
         <v>95</v>
       </c>
+      <c r="R228" t="n">
+        <v>0.2217553688141924</v>
+      </c>
       <c r="S228" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U228" t="inlineStr">
@@ -45225,9 +45567,12 @@
       <c r="O230" t="n">
         <v>1702</v>
       </c>
+      <c r="R230" t="n">
+        <v>3.972922502334267</v>
+      </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U230" t="inlineStr">
@@ -45615,9 +45960,12 @@
       <c r="O232" t="n">
         <v>3208</v>
       </c>
+      <c r="R232" t="n">
+        <v>7.488328664799253</v>
+      </c>
       <c r="S232" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U232" t="inlineStr">
@@ -46005,9 +46353,12 @@
       <c r="O234" t="n">
         <v>277</v>
       </c>
+      <c r="R234" t="n">
+        <v>0.6465919701213818</v>
+      </c>
       <c r="S234" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U234" t="inlineStr">
@@ -46395,9 +46746,12 @@
       <c r="O236" t="n">
         <v>28</v>
       </c>
+      <c r="R236" t="n">
+        <v>0.06535947712418301</v>
+      </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U236" t="inlineStr">
@@ -46785,9 +47139,12 @@
       <c r="O238" t="n">
         <v>567</v>
       </c>
+      <c r="R238" t="n">
+        <v>1.323529411764706</v>
+      </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U238" t="inlineStr">
@@ -47175,9 +47532,12 @@
       <c r="O240" t="n">
         <v>216</v>
       </c>
+      <c r="R240" t="n">
+        <v>0.5042016806722689</v>
+      </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U240" t="inlineStr">
@@ -47565,9 +47925,12 @@
       <c r="O242" t="n">
         <v>5</v>
       </c>
+      <c r="R242" t="n">
+        <v>0.01167133520074697</v>
+      </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U242" t="inlineStr">
@@ -47955,9 +48318,12 @@
       <c r="O244" t="n">
         <v>835</v>
       </c>
+      <c r="R244" t="n">
+        <v>1.949112978524743</v>
+      </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U244" t="inlineStr">
@@ -48345,9 +48711,12 @@
       <c r="O246" t="n">
         <v>23</v>
       </c>
+      <c r="R246" t="n">
+        <v>0.05368814192343604</v>
+      </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U246" t="inlineStr">
@@ -48735,9 +49104,12 @@
       <c r="O248" t="n">
         <v>23</v>
       </c>
+      <c r="R248" t="n">
+        <v>0.05368814192343604</v>
+      </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U248" t="inlineStr">
@@ -49125,9 +49497,12 @@
       <c r="O250" t="n">
         <v>1229</v>
       </c>
+      <c r="R250" t="n">
+        <v>2.868814192343604</v>
+      </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U250" t="inlineStr">
@@ -49515,9 +49890,12 @@
       <c r="O252" t="n">
         <v>16</v>
       </c>
+      <c r="R252" t="n">
+        <v>0.03734827264239029</v>
+      </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U252" t="inlineStr">
@@ -49905,9 +50283,12 @@
       <c r="O254" t="n">
         <v>5</v>
       </c>
+      <c r="R254" t="n">
+        <v>0.01167133520074697</v>
+      </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U254" t="inlineStr">
@@ -50295,9 +50676,12 @@
       <c r="O256" t="n">
         <v>319</v>
       </c>
+      <c r="R256" t="n">
+        <v>0.7446311858076564</v>
+      </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U256" t="inlineStr">
@@ -50685,9 +51069,12 @@
       <c r="O258" t="n">
         <v>3145</v>
       </c>
+      <c r="R258" t="n">
+        <v>7.341269841269841</v>
+      </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U258" t="inlineStr">
@@ -51075,9 +51462,12 @@
       <c r="O260" t="n">
         <v>50</v>
       </c>
+      <c r="R260" t="n">
+        <v>0.1167133520074697</v>
+      </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U260" t="inlineStr">
@@ -51465,9 +51855,12 @@
       <c r="O262" t="n">
         <v>14</v>
       </c>
+      <c r="R262" t="n">
+        <v>0.03267973856209151</v>
+      </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U262" t="inlineStr">
@@ -51855,9 +52248,12 @@
       <c r="O264" t="n">
         <v>15</v>
       </c>
+      <c r="R264" t="n">
+        <v>0.0350140056022409</v>
+      </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U264" t="inlineStr">
@@ -52245,9 +52641,12 @@
       <c r="O266" t="n">
         <v>1</v>
       </c>
+      <c r="R266" t="n">
+        <v>0.002334267040149393</v>
+      </c>
       <c r="S266" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U266" t="inlineStr">
@@ -52635,9 +53034,12 @@
       <c r="O268" t="n">
         <v>1937</v>
       </c>
+      <c r="R268" t="n">
+        <v>4.521475256769374</v>
+      </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U268" t="inlineStr">
@@ -53025,9 +53427,12 @@
       <c r="O270" t="n">
         <v>3356</v>
       </c>
+      <c r="R270" t="n">
+        <v>7.833800186741364</v>
+      </c>
       <c r="S270" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U270" t="inlineStr">
@@ -53415,9 +53820,12 @@
       <c r="O272" t="n">
         <v>250</v>
       </c>
+      <c r="R272" t="n">
+        <v>0.5835667600373482</v>
+      </c>
       <c r="S272" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U272" t="inlineStr">
@@ -53805,9 +54213,12 @@
       <c r="O274" t="n">
         <v>22</v>
       </c>
+      <c r="R274" t="n">
+        <v>0.05135387488328665</v>
+      </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U274" t="inlineStr">
@@ -54195,9 +54606,12 @@
       <c r="O276" t="n">
         <v>1</v>
       </c>
+      <c r="R276" t="n">
+        <v>0.002334267040149393</v>
+      </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U276" t="inlineStr">
@@ -54585,9 +54999,12 @@
       <c r="O278" t="n">
         <v>558</v>
       </c>
+      <c r="R278" t="n">
+        <v>1.302521008403361</v>
+      </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U278" t="inlineStr">
@@ -54975,9 +55392,12 @@
       <c r="O280" t="n">
         <v>188</v>
       </c>
+      <c r="R280" t="n">
+        <v>0.4388422035480858</v>
+      </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U280" t="inlineStr">
@@ -55365,9 +55785,12 @@
       <c r="O282" t="n">
         <v>2</v>
       </c>
+      <c r="R282" t="n">
+        <v>0.004668534080298786</v>
+      </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U282" t="inlineStr">
@@ -55755,9 +56178,12 @@
       <c r="O284" t="n">
         <v>345</v>
       </c>
+      <c r="R284" t="n">
+        <v>0.8053221288515405</v>
+      </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U284" t="inlineStr">
@@ -56145,9 +56571,12 @@
       <c r="O286" t="n">
         <v>23</v>
       </c>
+      <c r="R286" t="n">
+        <v>0.05368814192343604</v>
+      </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U286" t="inlineStr">
@@ -56535,9 +56964,12 @@
       <c r="O288" t="n">
         <v>25</v>
       </c>
+      <c r="R288" t="n">
+        <v>0.05835667600373483</v>
+      </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U288" t="inlineStr">
@@ -56925,9 +57357,12 @@
       <c r="O290" t="n">
         <v>1261</v>
       </c>
+      <c r="R290" t="n">
+        <v>2.943510737628385</v>
+      </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U290" t="inlineStr">
@@ -57315,9 +57750,12 @@
       <c r="O292" t="n">
         <v>7</v>
       </c>
+      <c r="R292" t="n">
+        <v>0.01633986928104575</v>
+      </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U292" t="inlineStr">
@@ -57705,9 +58143,12 @@
       <c r="O294" t="n">
         <v>3</v>
       </c>
+      <c r="R294" t="n">
+        <v>0.00700280112044818</v>
+      </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U294" t="inlineStr">
@@ -58095,9 +58536,12 @@
       <c r="O296" t="n">
         <v>285</v>
       </c>
+      <c r="R296" t="n">
+        <v>0.665266106442577</v>
+      </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U296" t="inlineStr">
@@ -58485,9 +58929,12 @@
       <c r="O298" t="n">
         <v>2576</v>
       </c>
+      <c r="R298" t="n">
+        <v>6.013071895424837</v>
+      </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U298" t="inlineStr">
@@ -58875,9 +59322,12 @@
       <c r="O300" t="n">
         <v>63</v>
       </c>
+      <c r="R300" t="n">
+        <v>0.1470588235294118</v>
+      </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U300" t="inlineStr">
@@ -59265,9 +59715,12 @@
       <c r="O302" t="n">
         <v>15</v>
       </c>
+      <c r="R302" t="n">
+        <v>0.0350140056022409</v>
+      </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U302" t="inlineStr">
@@ -59655,9 +60108,12 @@
       <c r="O304" t="n">
         <v>1</v>
       </c>
+      <c r="R304" t="n">
+        <v>0.002334267040149393</v>
+      </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U304" t="inlineStr">
@@ -60045,9 +60501,12 @@
       <c r="O306" t="n">
         <v>1975</v>
       </c>
+      <c r="R306" t="n">
+        <v>4.610177404295052</v>
+      </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U306" t="inlineStr">
@@ -60435,9 +60894,12 @@
       <c r="O308" t="n">
         <v>3114</v>
       </c>
+      <c r="R308" t="n">
+        <v>7.26890756302521</v>
+      </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U308" t="inlineStr">
@@ -60825,9 +61287,12 @@
       <c r="O310" t="n">
         <v>205</v>
       </c>
+      <c r="R310" t="n">
+        <v>0.4785247432306256</v>
+      </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U310" t="inlineStr">
@@ -61215,9 +61680,12 @@
       <c r="O312" t="n">
         <v>13</v>
       </c>
+      <c r="R312" t="n">
+        <v>0.03034547152194211</v>
+      </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U312" t="inlineStr">
@@ -61605,9 +62073,12 @@
       <c r="O314" t="n">
         <v>1</v>
       </c>
+      <c r="R314" t="n">
+        <v>0.002334267040149393</v>
+      </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U314" t="inlineStr">
@@ -61995,9 +62466,12 @@
       <c r="O316" t="n">
         <v>531</v>
       </c>
+      <c r="R316" t="n">
+        <v>1.239495798319328</v>
+      </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U316" t="inlineStr">
@@ -62385,9 +62859,12 @@
       <c r="O318" t="n">
         <v>170</v>
       </c>
+      <c r="R318" t="n">
+        <v>0.3968253968253968</v>
+      </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U318" t="inlineStr">
@@ -62775,9 +63252,12 @@
       <c r="O320" t="n">
         <v>4</v>
       </c>
+      <c r="R320" t="n">
+        <v>0.009337068160597572</v>
+      </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U320" t="inlineStr">
@@ -63165,9 +63645,12 @@
       <c r="O322" t="n">
         <v>269</v>
       </c>
+      <c r="R322" t="n">
+        <v>0.6279178338001867</v>
+      </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U322" t="inlineStr">
@@ -63555,9 +64038,12 @@
       <c r="O324" t="n">
         <v>25</v>
       </c>
+      <c r="R324" t="n">
+        <v>0.05835667600373483</v>
+      </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U324" t="inlineStr">
@@ -63945,9 +64431,12 @@
       <c r="O326" t="n">
         <v>26</v>
       </c>
+      <c r="R326" t="n">
+        <v>0.06069094304388423</v>
+      </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U326" t="inlineStr">
@@ -64335,9 +64824,12 @@
       <c r="O328" t="n">
         <v>1003</v>
       </c>
+      <c r="R328" t="n">
+        <v>2.341269841269841</v>
+      </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U328" t="inlineStr">
@@ -64725,9 +65217,12 @@
       <c r="O330" t="n">
         <v>18</v>
       </c>
+      <c r="R330" t="n">
+        <v>0.04201680672268908</v>
+      </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U330" t="inlineStr">
@@ -65115,9 +65610,12 @@
       <c r="O332" t="n">
         <v>4</v>
       </c>
+      <c r="R332" t="n">
+        <v>0.009337068160597572</v>
+      </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U332" t="inlineStr">
@@ -65505,9 +66003,12 @@
       <c r="O334" t="n">
         <v>268</v>
       </c>
+      <c r="R334" t="n">
+        <v>0.6255835667600373</v>
+      </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U334" t="inlineStr">
@@ -65895,9 +66396,12 @@
       <c r="O336" t="n">
         <v>2751</v>
       </c>
+      <c r="R336" t="n">
+        <v>6.421568627450981</v>
+      </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U336" t="inlineStr">
@@ -66285,9 +66789,12 @@
       <c r="O338" t="n">
         <v>45</v>
       </c>
+      <c r="R338" t="n">
+        <v>0.1050420168067227</v>
+      </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U338" t="inlineStr">
@@ -66675,9 +67182,12 @@
       <c r="O340" t="n">
         <v>27</v>
       </c>
+      <c r="R340" t="n">
+        <v>0.06302521008403361</v>
+      </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U340" t="inlineStr">
@@ -67065,9 +67575,12 @@
       <c r="O342" t="n">
         <v>1</v>
       </c>
+      <c r="R342" t="n">
+        <v>0.002334267040149393</v>
+      </c>
       <c r="S342" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U342" t="inlineStr">
@@ -67455,9 +67968,12 @@
       <c r="O344" t="n">
         <v>1485</v>
       </c>
+      <c r="R344" t="n">
+        <v>3.466386554621849</v>
+      </c>
       <c r="S344" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U344" t="inlineStr">
@@ -67845,9 +68361,12 @@
       <c r="O346" t="n">
         <v>3047</v>
       </c>
+      <c r="R346" t="n">
+        <v>7.1125116713352</v>
+      </c>
       <c r="S346" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U346" t="inlineStr">
@@ -68235,9 +68754,12 @@
       <c r="O348" t="n">
         <v>418</v>
       </c>
+      <c r="R348" t="n">
+        <v>0.9757236227824464</v>
+      </c>
       <c r="S348" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U348" t="inlineStr">
@@ -68625,9 +69147,12 @@
       <c r="O350" t="n">
         <v>8</v>
       </c>
+      <c r="R350" t="n">
+        <v>0.01867413632119514</v>
+      </c>
       <c r="S350" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U350" t="inlineStr">
@@ -69015,9 +69540,12 @@
       <c r="O352" t="n">
         <v>1</v>
       </c>
+      <c r="R352" t="n">
+        <v>0.002334267040149393</v>
+      </c>
       <c r="S352" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U352" t="inlineStr">
@@ -69405,9 +69933,12 @@
       <c r="O354" t="n">
         <v>583</v>
       </c>
+      <c r="R354" t="n">
+        <v>1.360877684407096</v>
+      </c>
       <c r="S354" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U354" t="inlineStr">
@@ -69795,9 +70326,12 @@
       <c r="O356" t="n">
         <v>161</v>
       </c>
+      <c r="R356" t="n">
+        <v>0.3758169934640523</v>
+      </c>
       <c r="S356" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U356" t="inlineStr">
@@ -70185,9 +70719,12 @@
       <c r="O358" t="n">
         <v>2</v>
       </c>
+      <c r="R358" t="n">
+        <v>0.004668534080298786</v>
+      </c>
       <c r="S358" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U358" t="inlineStr">
@@ -70575,9 +71112,12 @@
       <c r="O360" t="n">
         <v>508</v>
       </c>
+      <c r="R360" t="n">
+        <v>1.185807656395892</v>
+      </c>
       <c r="S360" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U360" t="inlineStr">
@@ -70965,9 +71505,12 @@
       <c r="O362" t="n">
         <v>16</v>
       </c>
+      <c r="R362" t="n">
+        <v>0.03734827264239029</v>
+      </c>
       <c r="S362" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U362" t="inlineStr">
@@ -71355,9 +71898,12 @@
       <c r="O364" t="n">
         <v>17</v>
       </c>
+      <c r="R364" t="n">
+        <v>0.03968253968253968</v>
+      </c>
       <c r="S364" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U364" t="inlineStr">
@@ -71745,9 +72291,12 @@
       <c r="O366" t="n">
         <v>1926</v>
       </c>
+      <c r="R366" t="n">
+        <v>4.495798319327731</v>
+      </c>
       <c r="S366" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U366" t="inlineStr">
@@ -72135,9 +72684,12 @@
       <c r="O368" t="n">
         <v>45</v>
       </c>
+      <c r="R368" t="n">
+        <v>0.1050420168067227</v>
+      </c>
       <c r="S368" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U368" t="inlineStr">
@@ -72525,9 +73077,12 @@
       <c r="O370" t="n">
         <v>0</v>
       </c>
+      <c r="R370" t="n">
+        <v>0</v>
+      </c>
       <c r="S370" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U370" t="inlineStr">
@@ -72915,9 +73470,12 @@
       <c r="O372" t="n">
         <v>336</v>
       </c>
+      <c r="R372" t="n">
+        <v>0.7843137254901961</v>
+      </c>
       <c r="S372" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U372" t="inlineStr">
@@ -73305,9 +73863,12 @@
       <c r="O374" t="n">
         <v>2690</v>
       </c>
+      <c r="R374" t="n">
+        <v>6.279178338001868</v>
+      </c>
       <c r="S374" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U374" t="inlineStr">
@@ -73695,9 +74256,12 @@
       <c r="O376" t="n">
         <v>61</v>
       </c>
+      <c r="R376" t="n">
+        <v>0.142390289449113</v>
+      </c>
       <c r="S376" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U376" t="inlineStr">
@@ -74085,9 +74649,12 @@
       <c r="O378" t="n">
         <v>24</v>
       </c>
+      <c r="R378" t="n">
+        <v>0.05602240896358544</v>
+      </c>
       <c r="S378" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U378" t="inlineStr">
@@ -74475,9 +75042,12 @@
       <c r="O380" t="n">
         <v>1</v>
       </c>
+      <c r="R380" t="n">
+        <v>0.002334267040149393</v>
+      </c>
       <c r="S380" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U380" t="inlineStr">
@@ -74865,9 +75435,12 @@
       <c r="O382" t="n">
         <v>1050</v>
       </c>
+      <c r="R382" t="n">
+        <v>2.450980392156862</v>
+      </c>
       <c r="S382" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U382" t="inlineStr">
@@ -75255,9 +75828,12 @@
       <c r="O384" t="n">
         <v>2431</v>
       </c>
+      <c r="R384" t="n">
+        <v>5.674603174603175</v>
+      </c>
       <c r="S384" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U384" t="inlineStr">
@@ -75645,9 +76221,12 @@
       <c r="O386" t="n">
         <v>142</v>
       </c>
+      <c r="R386" t="n">
+        <v>0.3314659197012138</v>
+      </c>
       <c r="S386" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U386" t="inlineStr">
@@ -76035,9 +76614,12 @@
       <c r="O388" t="n">
         <v>10</v>
       </c>
+      <c r="R388" t="n">
+        <v>0.02334267040149393</v>
+      </c>
       <c r="S388" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U388" t="inlineStr">
@@ -76425,9 +77007,12 @@
       <c r="O390" t="n">
         <v>3</v>
       </c>
+      <c r="R390" t="n">
+        <v>0.00700280112044818</v>
+      </c>
       <c r="S390" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U390" t="inlineStr">
@@ -76815,9 +77400,12 @@
       <c r="O392" t="n">
         <v>479</v>
       </c>
+      <c r="R392" t="n">
+        <v>1.118113912231559</v>
+      </c>
       <c r="S392" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U392" t="inlineStr">
@@ -77205,9 +77793,12 @@
       <c r="O394" t="n">
         <v>133</v>
       </c>
+      <c r="R394" t="n">
+        <v>0.3104575163398693</v>
+      </c>
       <c r="S394" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U394" t="inlineStr">
@@ -77595,9 +78186,12 @@
       <c r="O396" t="n">
         <v>2</v>
       </c>
+      <c r="R396" t="n">
+        <v>0.004668534080298786</v>
+      </c>
       <c r="S396" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U396" t="inlineStr">
@@ -77985,9 +78579,12 @@
       <c r="O398" t="n">
         <v>581</v>
       </c>
+      <c r="R398" t="n">
+        <v>1.356209150326797</v>
+      </c>
       <c r="S398" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U398" t="inlineStr">
@@ -78375,9 +78972,12 @@
       <c r="O400" t="n">
         <v>10</v>
       </c>
+      <c r="R400" t="n">
+        <v>0.02334267040149393</v>
+      </c>
       <c r="S400" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U400" t="inlineStr">
@@ -78765,9 +79365,12 @@
       <c r="O402" t="n">
         <v>11</v>
       </c>
+      <c r="R402" t="n">
+        <v>0.02567693744164333</v>
+      </c>
       <c r="S402" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U402" t="inlineStr">
@@ -79155,9 +79758,12 @@
       <c r="O404" t="n">
         <v>1478</v>
       </c>
+      <c r="R404" t="n">
+        <v>3.450046685340803</v>
+      </c>
       <c r="S404" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U404" t="inlineStr">
@@ -79545,9 +80151,12 @@
       <c r="O406" t="n">
         <v>79</v>
       </c>
+      <c r="R406" t="n">
+        <v>0.1844070961718021</v>
+      </c>
       <c r="S406" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U406" t="inlineStr">
@@ -79935,9 +80544,12 @@
       <c r="O408" t="n">
         <v>0</v>
       </c>
+      <c r="R408" t="n">
+        <v>0</v>
+      </c>
       <c r="S408" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U408" t="inlineStr">
@@ -80325,9 +80937,12 @@
       <c r="O410" t="n">
         <v>269</v>
       </c>
+      <c r="R410" t="n">
+        <v>0.6279178338001867</v>
+      </c>
       <c r="S410" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U410" t="inlineStr">
@@ -80715,9 +81330,12 @@
       <c r="O412" t="n">
         <v>1937</v>
       </c>
+      <c r="R412" t="n">
+        <v>4.521475256769374</v>
+      </c>
       <c r="S412" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U412" t="inlineStr">
@@ -81105,9 +81723,12 @@
       <c r="O414" t="n">
         <v>51</v>
       </c>
+      <c r="R414" t="n">
+        <v>0.119047619047619</v>
+      </c>
       <c r="S414" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U414" t="inlineStr">
@@ -81495,9 +82116,12 @@
       <c r="O416" t="n">
         <v>9</v>
       </c>
+      <c r="R416" t="n">
+        <v>0.02100840336134454</v>
+      </c>
       <c r="S416" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U416" t="inlineStr">
@@ -81885,9 +82509,12 @@
       <c r="O418" t="n">
         <v>522</v>
       </c>
+      <c r="R418" t="n">
+        <v>1.218487394957983</v>
+      </c>
       <c r="S418" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U418" t="inlineStr">
@@ -82275,9 +82902,12 @@
       <c r="O420" t="n">
         <v>1417</v>
       </c>
+      <c r="R420" t="n">
+        <v>3.30765639589169</v>
+      </c>
       <c r="S420" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U420" t="inlineStr">
@@ -82665,9 +83295,12 @@
       <c r="O422" t="n">
         <v>65</v>
       </c>
+      <c r="R422" t="n">
+        <v>0.1517273576097105</v>
+      </c>
       <c r="S422" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U422" t="inlineStr">
@@ -83055,9 +83688,12 @@
       <c r="O424" t="n">
         <v>4</v>
       </c>
+      <c r="R424" t="n">
+        <v>0.009337068160597572</v>
+      </c>
       <c r="S424" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U424" t="inlineStr">
@@ -83445,9 +84081,12 @@
       <c r="O426" t="n">
         <v>2</v>
       </c>
+      <c r="R426" t="n">
+        <v>0.004668534080298786</v>
+      </c>
       <c r="S426" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U426" t="inlineStr">
@@ -83835,9 +84474,12 @@
       <c r="O428" t="n">
         <v>368</v>
       </c>
+      <c r="R428" t="n">
+        <v>0.8590102707749766</v>
+      </c>
       <c r="S428" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U428" t="inlineStr">
@@ -84225,9 +84867,12 @@
       <c r="O430" t="n">
         <v>114</v>
       </c>
+      <c r="R430" t="n">
+        <v>0.2661064425770308</v>
+      </c>
       <c r="S430" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U430" t="inlineStr">
@@ -84615,9 +85260,12 @@
       <c r="O432" t="n">
         <v>1</v>
       </c>
+      <c r="R432" t="n">
+        <v>0.002334267040149393</v>
+      </c>
       <c r="S432" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U432" t="inlineStr">
@@ -85005,9 +85653,12 @@
       <c r="O434" t="n">
         <v>674</v>
       </c>
+      <c r="R434" t="n">
+        <v>1.573295985060691</v>
+      </c>
       <c r="S434" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U434" t="inlineStr">
@@ -85395,9 +86046,12 @@
       <c r="O436" t="n">
         <v>18</v>
       </c>
+      <c r="R436" t="n">
+        <v>0.04201680672268908</v>
+      </c>
       <c r="S436" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U436" t="inlineStr">
@@ -85785,9 +86439,12 @@
       <c r="O438" t="n">
         <v>9</v>
       </c>
+      <c r="R438" t="n">
+        <v>0.02100840336134454</v>
+      </c>
       <c r="S438" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U438" t="inlineStr">
@@ -86175,9 +86832,12 @@
       <c r="O440" t="n">
         <v>1201</v>
       </c>
+      <c r="R440" t="n">
+        <v>2.803454715219421</v>
+      </c>
       <c r="S440" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U440" t="inlineStr">
@@ -86565,9 +87225,12 @@
       <c r="O442" t="n">
         <v>46</v>
       </c>
+      <c r="R442" t="n">
+        <v>0.1073762838468721</v>
+      </c>
       <c r="S442" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U442" t="inlineStr">
